--- a/config.xlsx
+++ b/config.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shops" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Enemies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Items" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vehicles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Maps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NPCs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Skills" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Shops" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Quests" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1394,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1404,6 +1404,10 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1442,6 +1446,26 @@
           <t>音乐</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>无限地图</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>是否城镇</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>入口X</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>入口Y</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1471,6 +1495,22 @@
           <t>battle_wild.mp3</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1500,6 +1540,22 @@
           <t>town_theme.mp3</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1529,6 +1585,22 @@
           <t>town_theme2.mp3</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1558,6 +1630,22 @@
           <t>industrial.mp3</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1586,6 +1674,22 @@
         <is>
           <t>dungeon.mp3</t>
         </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,8 @@
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +484,11 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>区域ID</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -517,7 +523,10 @@
       <c r="I2" t="n">
         <v>0.3</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>凶猛的野狗，经常成群结队出现</t>
         </is>
@@ -553,7 +562,10 @@
       <c r="I3" t="n">
         <v>0.25</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>拦路抢劫的恶棍，装备简陋武器</t>
         </is>
@@ -589,7 +601,10 @@
       <c r="I4" t="n">
         <v>0.2</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>覆盖厚重装甲的昆虫，防御极高</t>
         </is>
@@ -625,7 +640,10 @@
       <c r="I5" t="n">
         <v>0.1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>废弃的战争机器，火力强大</t>
         </is>
@@ -661,7 +679,10 @@
       <c r="I6" t="n">
         <v>0.35</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>体型小速度快的啮齿动物</t>
         </is>
@@ -697,7 +718,10 @@
       <c r="I7" t="n">
         <v>0.15</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>专业的赏金猎人，战斗力强</t>
         </is>
@@ -733,7 +757,10 @@
       <c r="I8" t="n">
         <v>0.08</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>巨大的机械蝎子，尾部有剧毒</t>
         </is>
@@ -769,7 +796,10 @@
       <c r="I9" t="n">
         <v>0.05</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>诺亚系统的碎片，终极BOSS</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -2348,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2359,6 +2359,7 @@
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2389,15 +2390,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>目标数量</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>奖励经验</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>奖励金币</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>奖励物品</t>
         </is>
@@ -2426,12 +2432,15 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>200</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2457,15 +2466,18 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>500</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2491,15 +2503,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>150</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>300</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2525,15 +2540,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>300</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>800</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>9</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1996,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2004,7 +2004,8 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2035,6 +2036,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>解锁等级</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -2061,7 +2067,10 @@
           <t>造成物理伤害</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>基础的物理攻击</t>
         </is>
@@ -2089,7 +2098,10 @@
           <t>蓄力一击，伤害翻倍</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>需要一回合蓄力的强力攻击</t>
         </is>
@@ -2117,7 +2129,10 @@
           <t>减少受到的伤害</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>暂时提高防御力</t>
         </is>
@@ -2145,7 +2160,10 @@
           <t>提高闪避率</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>暂时提高闪避率</t>
         </is>
@@ -2173,7 +2191,10 @@
           <t>无视防御的强力攻击</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>消耗大量能量的终极技能</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -824,8 +824,9 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,10 +857,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>装备槽位</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>战斗中可用</t>
         </is>
@@ -885,12 +891,13 @@
       <c r="E2" t="n">
         <v>50</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>恢复30点HP</t>
         </is>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -914,12 +921,13 @@
       <c r="E3" t="n">
         <v>200</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>完全恢复HP</t>
         </is>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -943,12 +951,13 @@
       <c r="E4" t="n">
         <v>150</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>暂时提升攻击力</t>
         </is>
       </c>
-      <c r="G4" t="b">
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -974,10 +983,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>基础远程武器，攻击力+20</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1003,10 +1017,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>高科技激光武器，攻击力+35</t>
         </is>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1032,10 +1051,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>重型反装甲武器，攻击力+50</t>
         </is>
       </c>
-      <c r="G7" t="b">
+      <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1061,10 +1085,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>基础头部防护，防御力+10</t>
         </is>
       </c>
-      <c r="G8" t="b">
+      <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1090,10 +1119,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>身</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>军用防弹背心，防御力+25</t>
         </is>
       </c>
-      <c r="G9" t="b">
+      <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1119,10 +1153,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>身</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>外骨骼动力装甲，防御力+40</t>
         </is>
       </c>
-      <c r="G10" t="b">
+      <c r="H10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1146,12 +1185,13 @@
       <c r="E11" t="n">
         <v>100</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>恢复战车50点燃料</t>
         </is>
       </c>
-      <c r="G11" t="b">
+      <c r="H11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -433,7 +433,9 @@
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +491,16 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>掉落物品ID</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>掉落率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -526,7 +538,13 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>凶猛的野狗，经常成群结队出现</t>
         </is>
@@ -565,7 +583,13 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>拦路抢劫的恶棍，装备简陋武器</t>
         </is>
@@ -604,7 +628,13 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>覆盖厚重装甲的昆虫，防御极高</t>
         </is>
@@ -643,7 +673,13 @@
       <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>废弃的战争机器，火力强大</t>
         </is>
@@ -682,7 +718,13 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>体型小速度快的啮齿动物</t>
         </is>
@@ -721,7 +763,13 @@
       <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>专业的赏金猎人，战斗力强</t>
         </is>
@@ -760,7 +808,13 @@
       <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>巨大的机械蝎子，尾部有剧毒</t>
         </is>
@@ -799,7 +853,13 @@
       <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>诺亚系统的碎片，终极BOSS</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Skills" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Shops" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Quests" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bounties" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,22 +421,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,15 +493,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>是否赏金首</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>掉落物品ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>掉落率</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -538,13 +545,18 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.25</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>凶猛的野狗，经常成群结队出现</t>
         </is>
@@ -583,13 +595,18 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.2</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>拦路抢劫的恶棍，装备简陋武器</t>
         </is>
@@ -628,13 +645,18 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>覆盖厚重装甲的昆虫，防御极高</t>
         </is>
@@ -673,13 +695,18 @@
       <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.4</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>废弃的战争机器，火力强大</t>
         </is>
@@ -718,13 +745,18 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.15</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>体型小速度快的啮齿动物</t>
         </is>
@@ -763,13 +795,18 @@
       <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>专业的赏金猎人，战斗力强</t>
         </is>
@@ -808,13 +845,18 @@
       <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.35</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>巨大的机械蝎子，尾部有剧毒</t>
         </is>
@@ -853,15 +895,570 @@
       <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.5</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>诺亚系统的碎片，终极BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>水怪</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>200</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>潜伏在水边的巨型变异生物，初出茅庐的赏金猎人试刀对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>水鬼</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>120</v>
+      </c>
+      <c r="H11" t="n">
+        <v>400</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>盘踞桥下的伏击者，动作诡诈，擅长偷袭过路旅人</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>马歇尔</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" t="n">
+        <v>800</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>盘踞废弃医院的暴徒，只接受一对一的决斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>大象</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>260</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>厚重如山的巨兽，皮糙肉厚，一身穷横之力</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>神秘人</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>800</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>没人见过他的真面目，出手极快，见势不妙就会逃走</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蜈蚣</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>420</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>盘踞山洞的多足怪物，甲壳坚硬如铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>戈麦斯</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>杀害红狼的凶手，开着战车的恶棍，卑鄙而强大</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>弗朗</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>650</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>从垃圾场里爬出来的畸巨体，浑身散发着腐臭与毒气</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>波特</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>800</v>
+      </c>
+      <c r="D18" t="n">
+        <v>52</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>水怪的远亲，体型更巨，老练的猎人也不愿轻易招惹</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>沙漠之舟</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62</v>
+      </c>
+      <c r="E19" t="n">
+        <v>38</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H19" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>沙漠中游荡的钢铁巨物，炮火轰鸣声便是旅人的丧钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>帕鲁</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D20" t="n">
+        <v>75</v>
+      </c>
+      <c r="E20" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>传说中赏金最高的通缉犯，洞穴中的魔王，只接受双脚应战的狂战士</t>
         </is>
       </c>
     </row>
@@ -2681,4 +3278,461 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>悬赏金额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>所在地图ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>坐标X</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>坐标Y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>敌人ID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>强制人战</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>水怪</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>潜伏在水边的巨型变异生物，初出茅庐的赏金猎人试刀对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>水鬼</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>盘踞桥下的伏击者，动作诡诈，擅长偷袭过路旅人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>马歇尔</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>盘踞废弃医院的暴徒，只接受一对一的决斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>大象</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>厚重如山的巨兽，皮糙肉厚，一身穷横之力</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>神秘人</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>没人见过他的真面目，出手极快，见势不妙就会逃走</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>蜈蚣</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>盘踞山洞的多足怪物，甲壳坚硬如铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>戈麦斯</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>杀害红狼的凶手，开着战车的恶棍，卑鄙而强大</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>弗朗</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>81500</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>从垃圾场里爬出来的畸巨体，浑身散发着腐臭与毒气</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>波特</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99800</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>水怪的远亲，体型更巨，老练的猎人也不愿轻易招惹</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>沙漠之舟</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>沙漠中游荡的钢铁巨物，炮火轰鸣声便是旅人的丧钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>帕鲁</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>传说中赏金最高的通缉犯，洞穴中的魔王，只接受双脚应战的狂战士</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config.xlsx
+++ b/config.xlsx
@@ -9,13 +9,17 @@
   <sheets>
     <sheet name="Enemies" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Items" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Vehicles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Maps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPCs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Skills" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Shops" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Quests" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Bounties" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Chassis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Engines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CUnits" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Weapons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vehicles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Maps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPCs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Skills" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Shops" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Quests" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1467,6 +1471,1056 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>解锁等级</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>普通攻击</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>造成物理伤害</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>基础的物理攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>蓄力射击</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>蓄力一击，伤害翻倍</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>需要一回合蓄力的强力攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>防御姿态</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>暂时提高防御力</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>紧急回避</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>evade</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>提高闪避率</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>暂时提高闪避率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>必杀技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>无视防御的强力攻击</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>消耗大量能量的终极技能</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>地图ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>商品列表</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>价格倍数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>伊尔镇商店</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>罗克镇武器店</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3,4,5</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>索鲁镇防具店</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,5,6,7</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>黑市</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>black_market</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,6,7,8,9</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>目标ID</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>目标数量</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>奖励经验</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>奖励金币</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>奖励物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>清理野犬</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kill</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>镇外的野犬威胁到了居民安全，请消灭它们。</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>消灭赏金猎人</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kill</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>一个危险的赏金猎人在附近活动，请将其消灭。</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="n">
+        <v>500</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>找回被盗物品</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>collect</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>我的传家宝被偷了，请帮我找回来。</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>调查地下遗迹</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>explore</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>地下遗迹可能有诺亚的线索，去调查一下。</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>800</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>悬赏金额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>所在地图ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>坐标X</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>坐标Y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>敌人ID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>强制人战</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>水怪</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>潜伏在水边的巨型变异生物，初出茅庐的赏金猎人试刀对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>水鬼</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>盘踞桥下的伏击者，动作诡诈，擅长偷袭过路旅人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>马歇尔</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>盘踞废弃医院的暴徒，只接受一对一的决斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>大象</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>厚重如山的巨兽，皮糙肉厚，一身穷横之力</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>神秘人</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>没人见过他的真面目，出手极快，见势不妙就会逃走</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>蜈蚣</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>盘踞山洞的多足怪物，甲壳坚硬如铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>戈麦斯</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>杀害红狼的凶手，开着战车的恶棍，卑鄙而强大</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>弗朗</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>81500</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>从垃圾场里爬出来的畸巨体，浑身散发着腐臭与毒气</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>波特</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99800</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>水怪的远亲，体型更巨，老练的猎人也不愿轻易招惹</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>沙漠之舟</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>沙漠中游荡的钢铁巨物，炮火轰鸣声便是旅人的丧钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>帕鲁</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>传说中赏金最高的通缉犯，洞穴中的魔王，只接受双脚应战的狂战士</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1863,19 +2917,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1891,37 +2945,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>耐久</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>底盘防御</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>防御上限</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>自重</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>燃料容量</t>
+          <t>主炮孔</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>燃料消耗</t>
+          <t>副炮孔</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>修理费用</t>
+          <t>SE孔</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1936,33 +2990,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>吉普车</t>
+          <t>蚊式</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>10.84</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>轻型侦察车辆，机动性好</t>
+          <t>最初的战车，底盘极轻，可堆大量装甲片</t>
         </is>
       </c>
     </row>
@@ -1972,33 +3026,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>坦克</t>
+          <t>野驴</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>9.51</v>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>重型战斗车辆，火力强大</t>
+          <t>轻型越野底盘，机动性好</t>
         </is>
       </c>
     </row>
@@ -2008,33 +3062,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>摩托车</t>
+          <t>巴士</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>9.26</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>快速机动载具，适合侦察</t>
+          <t>救护车底盘，初始无攻击能力</t>
         </is>
       </c>
     </row>
@@ -2051,26 +3105,26 @@
         <v>350</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>14.96</v>
       </c>
       <c r="G5" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中型战斗车辆，攻守平衡</t>
+          <t>步兵战车底盘，攻守平衡</t>
         </is>
       </c>
     </row>
@@ -2080,33 +3134,141 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>越野车</t>
+          <t>豹式</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>野战坦克底盘，载重好</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>虎式</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>400</v>
+      </c>
+      <c r="D7" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" t="n">
+        <v>360</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>中型主战坦克，综合性能强</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R狼</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>450</v>
+      </c>
+      <c r="D8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="n">
+        <v>450</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>红狼的座驾，底盘防御极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>K虎</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>600</v>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
         <v>30</v>
       </c>
-      <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>110</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>150</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>全天候作战车辆，适应性强</t>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>重型主战坦克，防御全游戏最高</t>
         </is>
       </c>
     </row>
@@ -2116,6 +3278,1232 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>载重</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>自重</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MOT1轻型引擎</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>入门引擎，载重 20 吨</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MOT3吉普引擎</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>吉普车标配引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BUL1公牛引擎</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>公牛引擎，动力更足</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HUNO汗诺引擎</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>汗诺引擎，重型车常用</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V48金刚式</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>载重 52 吨的高级引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V100金刚式改</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D7" t="n">
+        <v>115</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>最强引擎，载重 58 吨</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>命中</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>防御</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>自重</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>艾米</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>入门火控装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>所罗门1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>140</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>中级火控，命中回避均衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>所罗门2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>高级火控，防御极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>打击者</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>160</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>高命中高回避的火控</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>自重</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>55炮</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>55</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>基础主炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>105加农炮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>中口径加农炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>165T型主炮</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>红狼车主炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>205加农炮</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>780</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>高级加农炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>220炮</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>最强主炮，800 攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15机关炮</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>副炮</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>红狼车副炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>格林炮</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>副炮</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>可打一群敌人的副炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09机关炮</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>副炮</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>中口径机关炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>火龙</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>副炮</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>355</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>大威力副炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>波坦</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>副炮</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>340</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>最轻最强副炮，340 攻击仅 0.1 吨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>托卢</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>760</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>红狼专有 S-E，一击必杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>截击</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>720</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>迎击型 S-E</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>撞击板</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>迎击板，可拦截敌人攻击</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>底盘ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>引擎ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>C装置ID</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>主炮ID列表</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>副炮ID列表</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SE_ID列表</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>装甲片</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>燃料容量</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>燃料消耗</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>修理费用</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>吉普车</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>轻型侦察车辆，机动性好</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>摩托车</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>80</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>50</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>快速机动载具，适合侦察</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>装甲车</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J4" t="n">
+        <v>120</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>中型战斗车辆，攻守平衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>坦克</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>150</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>重型战斗车辆，火力强大</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>越野车</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>110</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>150</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>全天候作战车辆，适应性强</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>红狼战车</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="n">
+        <v>150</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>400</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>红狼的遗物，165T 主炮 + 托卢 S-E</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>重型坦克</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>150</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>500</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>钢铁巨兽，220 炮 + 波坦副炮</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>警车</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>120</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>高命中高回避的巡逻座驾</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2424,7 +4812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2685,1054 +5073,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>解锁等级</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>普通攻击</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>造成物理伤害</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>基础的物理攻击</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>蓄力射击</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>蓄力一击，伤害翻倍</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>需要一回合蓄力的强力攻击</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>防御姿态</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>defense</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>减少受到的伤害</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>暂时提高防御力</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>紧急回避</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>evade</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>提高闪避率</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>暂时提高闪避率</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>必杀技</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>special</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>无视防御的强力攻击</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>消耗大量能量的终极技能</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>地图ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>商品列表</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>价格倍数</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>伊尔镇商店</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1,2,3,4</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>罗克镇武器店</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3,4,5</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>索鲁镇防具店</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4,5,6,7</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>黑市</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>black_market</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5,6,7,8,9</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>目标ID</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>目标数量</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>奖励经验</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>奖励金币</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>奖励物品</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>清理野犬</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>kill</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>镇外的野犬威胁到了居民安全，请消灭它们。</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" t="n">
-        <v>200</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>消灭赏金猎人</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>kill</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>一个危险的赏金猎人在附近活动，请将其消灭。</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>200</v>
-      </c>
-      <c r="H3" t="n">
-        <v>500</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>找回被盗物品</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>collect</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>我的传家宝被偷了，请帮我找回来。</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>150</v>
-      </c>
-      <c r="H4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>调查地下遗迹</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>explore</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>地下遗迹可能有诺亚的线索，去调查一下。</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>800</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>悬赏金额</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>所在地图ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>坐标X</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>坐标Y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>强制人战</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>水怪</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>潜伏在水边的巨型变异生物，初出茅庐的赏金猎人试刀对象</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>水鬼</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-12</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>盘踞桥下的伏击者，动作诡诈，擅长偷袭过路旅人</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>马歇尔</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>盘踞废弃医院的暴徒，只接受一对一的决斗</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>大象</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>厚重如山的巨兽，皮糙肉厚，一身穷横之力</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>神秘人</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>22000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>没人见过他的真面目，出手极快，见势不妙就会逃走</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>蜈蚣</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>35</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>盘踞山洞的多足怪物，甲壳坚硬如铁</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>戈麦斯</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>杀害红狼的凶手，开着战车的恶棍，卑鄙而强大</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>弗朗</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>81500</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G9" t="n">
-        <v>16</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>从垃圾场里爬出来的畸巨体，浑身散发着腐臭与毒气</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>波特</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>99800</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>26</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>水怪的远亲，体型更巨，老练的猎人也不愿轻易招惹</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>沙漠之舟</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>沙漠中游荡的钢铁巨物，炮火轰鸣声便是旅人的丧钟</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>帕鲁</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-45</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-42</v>
-      </c>
-      <c r="G12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>传说中赏金最高的通缉犯，洞穴中的魔王，只接受双脚应战的狂战士</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/config.xlsx
+++ b/config.xlsx
@@ -3283,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3291,7 +3291,8 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3322,6 +3323,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -3344,7 +3350,10 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>入门引擎，载重 20 吨</t>
         </is>
@@ -3368,7 +3377,10 @@
       <c r="E3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>吉普车标配引擎</t>
         </is>
@@ -3392,7 +3404,10 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>公牛引擎，动力更足</t>
         </is>
@@ -3416,7 +3431,10 @@
       <c r="E5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>汗诺引擎，重型车常用</t>
         </is>
@@ -3440,7 +3458,10 @@
       <c r="E6" t="n">
         <v>0.8</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>载重 52 吨的高级引擎</t>
         </is>
@@ -3464,7 +3485,10 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>最强引擎，载重 58 吨</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -438,10 +438,11 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,20 +498,25 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>系别</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>是否赏金首</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>掉落物品ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>掉落率</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -551,16 +557,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
       <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.25</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>凶猛的野狗，经常成群结队出现</t>
         </is>
@@ -601,16 +612,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>拦路抢劫的恶棍，装备简陋武器</t>
         </is>
@@ -651,16 +667,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>覆盖厚重装甲的昆虫，防御极高</t>
         </is>
@@ -701,16 +722,21 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>机械</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>废弃的战争机器，火力强大</t>
         </is>
@@ -751,16 +777,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
       <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.15</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>体型小速度快的啮齿动物</t>
         </is>
@@ -801,16 +832,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.3</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>专业的赏金猎人，战斗力强</t>
         </is>
@@ -851,16 +887,21 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>机械</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.35</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>巨大的机械蝎子，尾部有剧毒</t>
         </is>
@@ -901,16 +942,21 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>机械</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.5</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>诺亚系统的碎片，终极BOSS</t>
         </is>
@@ -951,16 +997,21 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>潜伏在水边的巨型变异生物，初出茅庐的赏金猎人试刀对象</t>
         </is>
@@ -1001,16 +1052,21 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
       <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>盘踞桥下的伏击者，动作诡诈，擅长偷袭过路旅人</t>
         </is>
@@ -1051,16 +1107,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.2</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>盘踞废弃医院的暴徒，只接受一对一的决斗</t>
         </is>
@@ -1101,16 +1162,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>厚重如山的巨兽，皮糙肉厚，一身穷横之力</t>
         </is>
@@ -1151,16 +1217,21 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.25</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>没人见过他的真面目，出手极快，见势不妙就会逃走</t>
         </is>
@@ -1201,16 +1272,21 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>8</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.15</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>盘踞山洞的多足怪物，甲壳坚硬如铁</t>
         </is>
@@ -1251,16 +1327,21 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.3</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>杀害红狼的凶手，开着战车的恶棍，卑鄙而强大</t>
         </is>
@@ -1301,16 +1382,21 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.3</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>从垃圾场里爬出来的畸巨体，浑身散发着腐臭与毒气</t>
         </is>
@@ -1351,16 +1437,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0.4</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>水怪的远亲，体型更巨，老练的猎人也不愿轻易招惹</t>
         </is>
@@ -1401,16 +1492,21 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>机械</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>10</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>沙漠中游荡的钢铁巨物，炮火轰鸣声便是旅人的丧钟</t>
         </is>
@@ -1451,16 +1547,21 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.5</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>传说中赏金最高的通缉犯，洞穴中的魔王，只接受双脚应战的狂战士</t>
         </is>
@@ -1699,7 +1800,7 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1754,7 +1855,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>1,2,10,16,17</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1780,7 +1881,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3,4,5</t>
+          <t>3,4,5,6,12,18,19</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1806,7 +1907,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4,5,6,7</t>
+          <t>7,8,9</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1832,7 +1933,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5,6,7,8,9</t>
+          <t>11,13,14,15</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2527,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2536,8 +2637,10 @@
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2573,10 +2676,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>使用场景</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>战斗中可用</t>
         </is>
@@ -2605,10 +2718,20 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>恢复30点HP</t>
         </is>
       </c>
-      <c r="H2" t="b">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2635,10 +2758,20 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>完全恢复HP</t>
         </is>
       </c>
-      <c r="H3" t="b">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2665,10 +2798,20 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>暂时提升攻击力</t>
         </is>
       </c>
-      <c r="H4" t="b">
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2697,12 +2840,14 @@
           <t>武器</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>基础远程武器，攻击力+20</t>
         </is>
       </c>
-      <c r="H5" t="b">
+      <c r="J5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2731,12 +2876,14 @@
           <t>武器</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>高科技激光武器，攻击力+35</t>
         </is>
       </c>
-      <c r="H6" t="b">
+      <c r="J6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2765,12 +2912,14 @@
           <t>武器</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>重型反装甲武器，攻击力+50</t>
         </is>
       </c>
-      <c r="H7" t="b">
+      <c r="J7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2799,12 +2948,14 @@
           <t>头</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>基础头部防护，防御力+10</t>
         </is>
       </c>
-      <c r="H8" t="b">
+      <c r="J8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2833,12 +2984,14 @@
           <t>身</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>军用防弹背心，防御力+25</t>
         </is>
       </c>
-      <c r="H9" t="b">
+      <c r="J9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2867,12 +3020,14 @@
           <t>身</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>外骨骼动力装甲，防御力+40</t>
         </is>
       </c>
-      <c r="H10" t="b">
+      <c r="J10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2899,10 +3054,380 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>车</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>恢复战车50点燃料</t>
         </is>
       </c>
-      <c r="H11" t="b">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>军号</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>buff_atkdef</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>夺命三宝之一，本场战斗攻防大幅提升（可能损坏）</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>烟幕弹</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="n">
+        <v>300</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>车</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>debuff_enemy</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>夺命三宝之一，本回合敌人伤害减半</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>雷达</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="n">
+        <v>500</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>车</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>buff_vehicle_atk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>夺命三宝之一，本场战车攻击提升</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>药液</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" t="n">
+        <v>400</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>damage_bio</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>腐蚀液，对生物系敌人造成重创</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>再生丸</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>完全恢复HP的珍贵药物</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>地图</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>map_hint</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>标记附近的城镇与赏金首方位</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>迷彩条</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>camouflage</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>踩雷（遇敌）率大幅下降，持续 30 次移动</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>铁弹</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E19" t="n">
+        <v>250</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>弹</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>damage_mech</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>特殊炮弹，对机械系敌人特效</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>钢弹</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>120</v>
+      </c>
+      <c r="E20" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>弹</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>damage_bio</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>燃烧弹，对生物系敌人特效</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Maps" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="NPCs" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Skills" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Shops" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Quests" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Bounties" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Classes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Shops" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Quests" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Bounties" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1578,16 +1579,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1618,10 +1622,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>解锁等级</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>职业限定</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>冷却</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -1649,10 +1668,17 @@
           <t>造成物理伤害</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>基础的物理攻击</t>
         </is>
@@ -1680,10 +1706,17 @@
           <t>蓄力一击，伤害翻倍</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>需要一回合蓄力的强力攻击</t>
         </is>
@@ -1711,10 +1744,17 @@
           <t>减少受到的伤害</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>暂时提高防御力</t>
         </is>
@@ -1742,10 +1782,17 @@
           <t>提高闪避率</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>暂时提高闪避率</t>
         </is>
@@ -1773,12 +1820,149 @@
           <t>无视防御的强力攻击</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>消耗大量能量的终极技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>电光石火</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>战车兵器连射两次</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>double_strike</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>猎人特技：同一战车兵器连续发射两次</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>紧急修理</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>恢复战车HP与装甲片</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair_vehicle</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>机械师特技：战斗中紧急抢修战车</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>肉搏精通</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>本场步行攻击大幅提升</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>melee_mastery</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>战士特技：步行战斗攻击提升</t>
         </is>
       </c>
     </row>
@@ -1788,6 +1972,168 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HP成长</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>攻击成长</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>防御成长</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>速度成长</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>特技</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>猎人</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>电光石火</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>专精战车战斗的赏金猎人，擅长连射武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>机械师</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>紧急修理</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>唯一能抢修战车的机械专家，乘车战斗好手</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>战士</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>肉搏精通</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>肉搏战专家，步行时攻击力成长最高</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1945,7 +2291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2165,7 +2511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/config.xlsx
+++ b/config.xlsx
@@ -4544,7 +4544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4552,7 +4552,8 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4583,6 +4584,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -4607,7 +4613,10 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>基础主炮</t>
         </is>
@@ -4633,7 +4642,10 @@
       <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>中口径加农炮</t>
         </is>
@@ -4659,9 +4671,12 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>红狼车主炮</t>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>红狼车主炮（专有，不出售）</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4700,10 @@
       <c r="E5" t="n">
         <v>3.1</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>高级加农炮</t>
         </is>
@@ -4711,7 +4729,10 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>最强主炮，800 攻击</t>
         </is>
@@ -4737,7 +4758,10 @@
       <c r="E7" t="n">
         <v>0.8</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>800</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>红狼车副炮</t>
         </is>
@@ -4763,7 +4787,10 @@
       <c r="E8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>可打一群敌人的副炮</t>
         </is>
@@ -4789,7 +4816,10 @@
       <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>中口径机关炮</t>
         </is>
@@ -4815,7 +4845,10 @@
       <c r="E10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>大威力副炮</t>
         </is>
@@ -4841,9 +4874,12 @@
       <c r="E11" t="n">
         <v>0.1</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>最轻最强副炮，340 攻击仅 0.1 吨</t>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>最轻最强副炮，340 攻击仅 0.1 吨（狙击车掉落）</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4903,10 @@
       <c r="E12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>红狼专有 S-E，一击必杀</t>
         </is>
@@ -4893,7 +4932,10 @@
       <c r="E13" t="n">
         <v>8.4</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>迎击型 S-E</t>
         </is>
@@ -4919,7 +4961,10 @@
       <c r="E14" t="n">
         <v>0.5</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>迎击板，可拦截敌人攻击</t>
         </is>

--- a/config.xlsx
+++ b/config.xlsx
@@ -4981,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4996,7 +4996,12 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5062,6 +5067,31 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>获取方式</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>获取X</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>获取Y</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>获取价格</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>获取条件</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -5105,7 +5135,24 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>轻型侦察车辆，机动性好</t>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>轻型侦察车辆，机动性好（初始座驾）</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5191,24 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>快速机动载具，适合侦察</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>快速机动载具，适合侦察（拉多附近山洞）</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5255,24 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>中型战斗车辆，攻守平衡</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>中型战斗车辆，攻守平衡（罗克镇外废墟）</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5323,24 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>重型战斗车辆，火力强大</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>重型战斗车辆，火力强大（索鲁下水道）</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5387,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>全天候作战车辆，适应性强</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" t="n">
+        <v>22</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>全天候作战车辆，适应性强（弗里海边洞窟）</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5455,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>红狼的遗物，165T 主炮 + 托卢 S-E</t>
+          <t>bounty</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>红狼的遗物，165T 主炮 + 托卢 S-E（击败戈麦斯继承）</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5523,24 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>钢铁巨兽，220 炮 + 波坦副炮</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-30</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>钢铁巨兽，220 炮 + 波坦副炮（卡拉兵工厂）</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5583,24 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>高命中高回避的巡逻座驾</t>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>高命中高回避的巡逻座驾（帕特港购买）</t>
         </is>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2284,6 +2284,32 @@
       </c>
       <c r="F5" t="n">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>迪斯顿枪械铺</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4,5,6,3</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -2297,13 +2323,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -2364,7 +2390,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>清理野犬</t>
+          <t>镇外的野犬</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2374,7 +2400,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>镇外的野犬威胁到了居民安全，请消灭它们。</t>
+          <t>镇外的野犬最近成群了，再不管管连羊都要被叼走。清掉三只。</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2401,7 +2427,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>消灭赏金猎人</t>
+          <t>失业的同行</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2411,7 +2437,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>一个危险的赏金猎人在附近活动，请将其消灭。</t>
+          <t>有个干我们这行的堕落成了拦路匪。赏金屋的规矩：同行不讲情面。</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2438,7 +2464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>找回被盗物品</t>
+          <t>被偷的传家宝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2448,7 +2474,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>我的传家宝被偷了，请帮我找回来。</t>
+          <t>传家宝猎枪被装甲虫拖进了洞。那玩意儿对铁皮有执念，杀虫取枪。</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2475,7 +2501,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>调查地下遗迹</t>
+          <t>遗迹调查</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2485,7 +2511,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>地下遗迹可能有诺亚的线索，去调查一下。</t>
+          <t>地下遗迹里有诺亚的线索。进去看一眼，活着回来就行。</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2503,6 +2529,154 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>迷之项圈</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>collect</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>弗里镇墨鸦悬赏：他丢了个"要紧的货"，恐怕被装甲虫刮走了。</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>诺亚的碎片</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kill</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>钢铁巨蝎的甲壳下藏着一块发光的碎片。霍卢夫的文徇先生出高价收。</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>沙漠护航</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kill</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>商队请猎人扫清去往卡拉的沙漠路。沙漠之舟会袭击一切带轮子的东西。</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>军医的托付</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>collect</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>卡拉镇的扳手需要一枚再生丸救一个流血不止的矿工。黑市有，但黑货不便宜。</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3775,6 +3949,42 @@
       </c>
       <c r="J20" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>宠物项圈</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>项圈上刻着"阿黄"。任务物品，交还给失主。</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5587,10 +5797,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
         <v>30000</v>
@@ -5615,7 +5825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5624,11 +5834,12 @@
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5687,6 +5898,11 @@
           <t>入口Y</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5731,6 +5947,11 @@
       </c>
       <c r="K2" t="n">
         <v>-1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>一望无际的锈色大地。文明的残骸埋在沙土里，赏金猎人开着战车追逐通缉犯。</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -5777,6 +5998,11 @@
       <c r="K3" t="n">
         <v>10</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>拉多山脚下的村落，一切旅程开始的地方。村口的老路灯据说是大破坏前的遗物。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5795,7 +6021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>城镇,港口,建筑</t>
+          <t>城镇,建筑,道路</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -5821,6 +6047,11 @@
       </c>
       <c r="K4" t="n">
         <v>-6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>以武器交易闻名的小镇，铁匠铺的炉火二十年没有熄过。</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5840,7 +6071,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>城镇,工厂,建筑</t>
+          <t>城镇,建筑,道路</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -5866,6 +6097,11 @@
       </c>
       <c r="K5" t="n">
         <v>-20</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>矿工聚居的镇子。下水道深处有奇怪的机械声，没人敢下去查。</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5893,7 +6129,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>dungeon.mp3</t>
+          <t>dungeon_theme.mp3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5911,6 +6147,361 @@
       </c>
       <c r="K6" t="n">
         <v>30</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>大破坏前的地下设施，自动炮塔还在运转。据说最深处有诺亚的碎片。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>梯克镇</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>城镇,建筑,道路</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>town_theme.mp3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>商队中转站，旅馆的酒馆里能听到天南海北的传闻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>帕特港</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>城镇,港口,建筑</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>port_theme.mp3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>48</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>曾经通往海洋的港口。海退走了，留下满岸的盐锈和一艘永不启航的干船坞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>弗里镇</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>城镇,建筑,道路</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>town_theme2.mp3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>不挂旗子的小镇。想要来路不明的货，就去找巷子尽头的墨鸦。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>卡拉镇</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>城镇,工厂,建筑</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>industrial.mp3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>-42</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>兵工厂遗址上建起的镇子，人人都会摆弄机械。后山还有没搬完的战争机器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>迪斯顿镇</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>城镇,建筑,道路</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>town_theme.mp3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>35</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>猎人聚居的镇子，墙上钉满了通缉令。枪械铺的老板娘眼力毒得很。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>霍卢夫镇</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>城镇,建筑,道路</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>town_theme2.mp3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-38</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>镇上的老人守着一座大破坏前的图书馆。他们记得世界还没有变成这样的时候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>神殿废墟</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>废墟,洞穴,机械</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>temple_theme.mp3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>诺亚神殿的残骸。地动不休，钢铁的嘶鸣声从地底传来——决战之地。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5924,13 +6515,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -5979,27 +6570,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>老人</t>
+          <t>村长·格雷姆</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>向导</t>
+          <t>村长</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>欢迎来到这个世界！小心外面的怪物。</t>
+          <t>欢迎来到伊尔镇，年轻人。出了村口就是荒野——带着战车去吧，徒步的人活不过三个昼夜。|[chapter&gt;=1]红狼夺走了你的副炮吧……这就是废土的规矩，强的吃弱的。别哭，去把它抢回来。|[chapter&gt;=3]你把戈麦斯干了？！红狼的在天之灵会保佑你的。孩子们都管你叫英雄了。</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -6008,7 +6599,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>商人</t>
+          <t>商人·老周</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6018,14 +6609,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>想买些什么吗？我有最好的装备！</t>
+          <t>药草、地图、迷彩条——荒野保命三件套，随便挑。</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -6037,27 +6628,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>机械师</t>
+          <t>铁匠·阿铁</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>修理工</t>
+          <t>武器商</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>需要修理战车吗？价格公道！</t>
+          <t>炉火二十年没熄过。你带来的废铁我全收。</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6066,27 +6657,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>赏金屋主人·罗刹</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>任务发布者</t>
+          <t>悬赏屋</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>听说附近有通缉犯，你能帮我解决吗？</t>
+          <t>墙上钉的是通缉令。按悬赏榜看名单，干掉的活儿别忘回来领赏。|[chapter&gt;=2]干得不错。赏金猎人这行，活着回来才能数钱。</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6095,27 +6686,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>镇长</t>
+          <t>酒馆老板·大壶</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>镇长</t>
+          <t>酒馆</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>我们的小镇很安全，请好好休息。</t>
+          <t>听说没？西边的老人说，大破坏前的机器夜里会自己亮灯。</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -6124,27 +6715,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>神秘女子</t>
+          <t>港口老板·海叔</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>神秘人物</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>命运之轮已经开始转动...</t>
+          <t>海退走了，船锈在这儿。要我说，这镇子就是个朝海的大坟场。|[chapter&gt;=4]神殿废墟地动个不停……老猎人们说得对，诺亚醒了。|[chapter&gt;=5]你要去神殿？带上再多的装甲片也不嫌多，去吧，猎人。</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -6153,27 +6744,230 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>博士</t>
+          <t>黑市商人·墨鸦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>科学家</t>
+          <t>黑市</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>诺亚系统已经失控，我们必须阻止它！</t>
+          <t>小点声。想要来路不明的货，报暗号：红狼走过的路。</t>
         </is>
       </c>
       <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>机械师·扳手</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>修理工</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>后山那些铁疙瘩还活着，我们年年拆，它们年年爬出来。</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>枪械铺老板娘·红姐</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>枪械铺</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>眼力毒才能在迪斯顿活下去。猎枪？我这儿只卖好枪。</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>老学者·文徇</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>学者</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>第三章·红狼。大破坏前的历史书只剩这一本……红狼不是强盗，孩子们，他是在替人类喂狼的守夜人。|[chapter&gt;=3]你也接过那杆炮了。听好了——戈麦斯欠红狼的，你替他还了。去神殿之前，来我这儿把旧世界的事听完。</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小孩·阿木</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>叔叔你的战车好大！能带我去荒野吗？</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>守墓人·老雷</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>守墓人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>镇外那些坟，一半埋的是猎人，一半埋的是没打完的仗。</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>拾荒者·半截</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>拾荒者</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>今天的收成不错——半截雷达，三根管子，一只不走的钟。</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>图书馆的回声</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>谜团</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>……诺……亚……觉醒……倒计时……[警告：访客，请离开]</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F15" t="n">
         <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -435,7 +435,7 @@
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
@@ -545,10 +545,10 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
         <v>0.3</v>
@@ -600,10 +600,10 @@
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="I3" t="n">
         <v>0.25</v>
@@ -655,10 +655,10 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I4" t="n">
         <v>0.2</v>
@@ -710,10 +710,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H5" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="I5" t="n">
         <v>0.1</v>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
         <v>0.35</v>
@@ -820,10 +820,10 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I7" t="n">
         <v>0.15</v>
@@ -875,10 +875,10 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
         <v>0.08</v>
@@ -930,10 +930,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H9" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="I9" t="n">
         <v>0.05</v>
@@ -985,10 +985,10 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="H11" t="n">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="H12" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1150,10 +1150,10 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="H13" t="n">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="H14" t="n">
-        <v>3000</v>
+        <v>4800</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1260,10 +1260,10 @@
         <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="H15" t="n">
-        <v>4500</v>
+        <v>7200</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1315,10 +1315,10 @@
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="H16" t="n">
-        <v>8000</v>
+        <v>12800</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="H17" t="n">
-        <v>12000</v>
+        <v>19200</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>3000</v>
+        <v>5500</v>
       </c>
       <c r="H18" t="n">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="D19" t="n">
         <v>62</v>
@@ -1480,10 +1480,10 @@
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>4500</v>
+        <v>8000</v>
       </c>
       <c r="H19" t="n">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="D20" t="n">
         <v>75</v>
@@ -1535,10 +1535,10 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H20" t="n">
-        <v>30000</v>
+        <v>48000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3159,7 +3159,7 @@
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>buff</t>
+          <t>buff_atk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3985,6 +3985,190 @@
       </c>
       <c r="J21" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>红镜片</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>传说中的四面镜之一，映着火光。集齐四片去找霍卢夫的文徇。</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>蓝镜片</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>传说中的四面镜之一，映着海色。集齐四片去找霍卢夫的文徇。</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>黄镜片</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>传说中的四面镜之一，映着沙金。集齐四片去找霍卢夫的文徇。</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>绿镜片</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>quest</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>探索</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>传说中的四面镜之一，映着苔绿。集齐四片去找霍卢夫的文徇。</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>兴奋剂Ⅱ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>40</v>
+      </c>
+      <c r="E26" t="n">
+        <v>600</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>buff_atk</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>精炼版兴奋剂，本场战斗攻击大幅提升</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4754,11 +4938,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
@@ -5177,6 +5361,35 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>迎击板，可拦截敌人攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4342型激光炮</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>主炮</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>四面镜合成的传说主炮，500 攻击（四镜片支线奖励）</t>
         </is>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -16,11 +16,12 @@
     <sheet name="Vehicles" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Maps" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="NPCs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Skills" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Classes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Shops" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Quests" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Bounties" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Partners" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Skills" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Classes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Shops" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Quests" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Bounties" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1579,6 +1580,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>招募NPC</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>招募条件</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>效果值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>机械师·克里夫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>机械师</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>卡拉兵工厂出身的机械师，一双巧手能让报废车回魂。（战斗结束后小修战车：装甲片+5，HP 恢复 10%）</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>退伍老兵·陈</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>格斗家</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>打了半辈子仗的老兵，肉搏功夫是荒野一绝。（徒步作战时攻击 +25%）</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>foot_atk</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1971,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2133,13 +2268,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2312,12 +2447,38 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>秘密商人</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>secret</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26,27,9,15,8</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2685,7 +2846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3148,14 +3309,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -4168,6 +4329,82 @@
         </is>
       </c>
       <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>火箭筒Ⅱ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>武器</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>重型火箭筒的改良型，攻击力+65（秘密商人独占）</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>军用口粮</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>150</v>
+      </c>
+      <c r="E28" t="n">
+        <v>800</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>军粮级压缩干粮，恢复150点HP（秘密商人独占）</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6038,7 +6275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6717,6 +6954,56 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>秘密基地</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>城镇,建筑,道路</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>town_theme2.mp3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>一处不存在的镇子。帆布和铁皮搭的棚子后面，堆着"不该存在的货"。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6728,7 +7015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7183,6 +7470,35 @@
         <v>11</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>退伍老兵·陈</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>格斗家</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>退下来以后一直在找能打仗的车。听说你干了戈麦斯？|[chapter&gt;=2]我这身手没处使，跟你的车走吧——徒步见真章的时候，你用得上我。|[flag:partner_2]跟你跑这一路，痛快。荒野才是老兵的家。</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
